--- a/summer_camps/014_summer_camp_reservation_form--summer_camps.xlsx
+++ b/summer_camps/014_summer_camp_reservation_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1067,34 +1067,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>camp_hours_choices</t>
+          <t>camp_duration_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8am-4pm</t>
+          <t>1_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8am-4pm</t>
+          <t>1 week</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>camp_hours_choices</t>
+          <t>camp_duration_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4pm-8pm</t>
+          <t>2_weeks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4pm-8pm</t>
+          <t>2 weeks</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1_week</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
@@ -1123,46 +1123,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2_weeks</t>
+          <t>2_months</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 weeks</t>
+          <t>2 months</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>camp_duration_choices</t>
+          <t>camp_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1_month</t>
+          <t>arts_and_crafts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Arts and Crafts</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>camp_duration_choices</t>
+          <t>camp_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2_months</t>
+          <t>music_and_movement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2 months</t>
+          <t>Music and Movement</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>arts_and_crafts</t>
+          <t>stem_education</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arts and Crafts</t>
+          <t>STEM Education</t>
         </is>
       </c>
     </row>
@@ -1191,46 +1191,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>music_and_movement</t>
+          <t>outdoor_adventures</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Music and Movement</t>
+          <t>Outdoor Adventures</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>camp_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stem_education</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STEM Education</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>camp_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>outdoor_adventures</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Outdoor Adventures</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1242,44 +1242,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>check</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>credit_card</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>paypal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>PayPal</t>
         </is>
